--- a/260911_휴머노이드 Job 할당 list 분석_v0.5_temp.xlsx
+++ b/260911_휴머노이드 Job 할당 list 분석_v0.5_temp.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'0907 (2)'!$B$3:$I$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'0907 (3)'!$B$3:$I$106</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -706,7 +706,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -831,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf applyNumberFormat="1" numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1537,15 +1540,15 @@
       <c r="F13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="3">
-        <v>1</v>
+      <c r="G13" s="44">
+        <v>0.38</v>
       </c>
       <c r="H13" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I13" s="12">
         <f>G13-H13</f>
-        <v>0.74199999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="J13" s="39"/>
       <c r="K13" s="12" t="s">
@@ -1573,15 +1576,15 @@
       <c r="F14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="3">
-        <v>3</v>
+      <c r="G14" s="44">
+        <v>2.54</v>
       </c>
       <c r="H14" s="12">
         <v>2.13</v>
       </c>
       <c r="I14" s="12">
         <f t="shared" ref="I14:I19" si="0">G14-H14</f>
-        <v>0.87000000000000011</v>
+        <v>0.41</v>
       </c>
       <c r="J14" s="39"/>
       <c r="K14" s="12" t="s">
@@ -1609,15 +1612,15 @@
       <c r="F15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="3">
-        <v>4</v>
+      <c r="G15" s="44">
+        <v>4.0</v>
       </c>
       <c r="H15" s="12">
         <v>1.28</v>
       </c>
       <c r="I15" s="37">
         <f t="shared" si="0"/>
-        <v>2.7199999999999998</v>
+        <v>2.72</v>
       </c>
       <c r="J15" s="39"/>
       <c r="K15" s="12" t="s">
@@ -1645,15 +1648,15 @@
       <c r="F16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="3">
-        <v>2</v>
+      <c r="G16" s="44">
+        <v>1.67</v>
       </c>
       <c r="H16" s="12">
         <v>0</v>
       </c>
       <c r="I16" s="12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="J16" s="39"/>
       <c r="K16" s="12" t="s">
@@ -1681,15 +1684,15 @@
       <c r="F17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="3">
-        <v>7</v>
+      <c r="G17" s="44">
+        <v>5.21</v>
       </c>
       <c r="H17" s="12">
         <v>0</v>
       </c>
       <c r="I17" s="37">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.21</v>
       </c>
       <c r="J17" s="39"/>
       <c r="K17" s="12" t="s">
@@ -1753,15 +1756,15 @@
       <c r="F19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="3">
-        <v>7</v>
+      <c r="G19" s="44">
+        <v>5.21</v>
       </c>
       <c r="H19" s="12">
         <v>2.13</v>
       </c>
       <c r="I19" s="37">
         <f t="shared" si="0"/>
-        <v>4.87</v>
+        <v>3.08</v>
       </c>
       <c r="J19" s="39"/>
       <c r="K19" s="12" t="s">
@@ -2113,15 +2116,15 @@
       <c r="F32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="3">
-        <v>5</v>
+      <c r="G32" s="44">
+        <v>4.72</v>
       </c>
       <c r="H32" s="12">
         <v>2.13</v>
       </c>
       <c r="I32" s="37">
         <f t="shared" ref="I32:I91" si="1">G32-H32</f>
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="J32" s="39"/>
       <c r="K32" s="12" t="s">
@@ -2149,15 +2152,15 @@
       <c r="F33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="3">
-        <v>1</v>
+      <c r="G33" s="44">
+        <v>0.38</v>
       </c>
       <c r="H33" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I33" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="J33" s="39"/>
       <c r="K33" s="12" t="s">
@@ -2185,15 +2188,15 @@
       <c r="F34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="3">
-        <v>2</v>
+      <c r="G34" s="44">
+        <v>1.67</v>
       </c>
       <c r="H34" s="12">
         <v>2.13</v>
       </c>
       <c r="I34" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>-0.46</v>
       </c>
       <c r="J34" s="39"/>
       <c r="K34" s="12" t="s">
@@ -2221,15 +2224,15 @@
       <c r="F35" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="3">
-        <v>3</v>
+      <c r="G35" s="44">
+        <v>2.79</v>
       </c>
       <c r="H35" s="12">
         <v>1.28</v>
       </c>
       <c r="I35" s="12">
         <f t="shared" si="1"/>
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="J35" s="39"/>
       <c r="K35" s="12" t="s">
@@ -2257,15 +2260,15 @@
       <c r="F36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="3">
-        <v>1</v>
+      <c r="G36" s="44">
+        <v>1.3</v>
       </c>
       <c r="H36" s="12">
         <v>0</v>
       </c>
       <c r="I36" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J36" s="39"/>
       <c r="K36" s="12" t="s">
@@ -2293,15 +2296,15 @@
       <c r="F37" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="3">
-        <v>7</v>
+      <c r="G37" s="44">
+        <v>5.21</v>
       </c>
       <c r="H37" s="12">
         <v>2.7</v>
       </c>
       <c r="I37" s="37">
         <f t="shared" si="1"/>
-        <v>4.3</v>
+        <v>2.51</v>
       </c>
       <c r="J37" s="39"/>
       <c r="K37" s="12" t="s">
@@ -2329,15 +2332,15 @@
       <c r="F38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G38" s="3">
-        <v>7</v>
+      <c r="G38" s="44">
+        <v>6.66</v>
       </c>
       <c r="H38" s="12">
         <v>1.28</v>
       </c>
       <c r="I38" s="37">
         <f t="shared" si="1"/>
-        <v>5.72</v>
+        <v>5.38</v>
       </c>
       <c r="J38" s="39"/>
       <c r="K38" s="12" t="s">
@@ -2365,15 +2368,15 @@
       <c r="F39" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="3">
-        <v>4</v>
+      <c r="G39" s="44">
+        <v>2.47</v>
       </c>
       <c r="H39" s="12">
         <v>2.13</v>
       </c>
       <c r="I39" s="12">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>0.34</v>
       </c>
       <c r="J39" s="39"/>
       <c r="K39" s="12" t="s">
@@ -2401,15 +2404,15 @@
       <c r="F40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="3">
-        <v>1</v>
+      <c r="G40" s="44">
+        <v>0.12</v>
       </c>
       <c r="H40" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I40" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>-0.138</v>
       </c>
       <c r="J40" s="39"/>
       <c r="K40" s="12" t="s">
@@ -2437,15 +2440,15 @@
       <c r="F41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="3">
-        <v>2</v>
+      <c r="G41" s="44">
+        <v>2.92</v>
       </c>
       <c r="H41" s="12">
         <v>2.13</v>
       </c>
       <c r="I41" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>0.79</v>
       </c>
       <c r="J41" s="39"/>
       <c r="K41" s="12" t="s">
@@ -2473,15 +2476,15 @@
       <c r="F42" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="3">
-        <v>3</v>
+      <c r="G42" s="44">
+        <v>2.78</v>
       </c>
       <c r="H42" s="12">
         <v>1.28</v>
       </c>
       <c r="I42" s="12">
         <f t="shared" si="1"/>
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="J42" s="39"/>
       <c r="K42" s="12" t="s">
@@ -2509,15 +2512,15 @@
       <c r="F43" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="3">
-        <v>2</v>
+      <c r="G43" s="44">
+        <v>2.62</v>
       </c>
       <c r="H43" s="12">
         <v>0</v>
       </c>
       <c r="I43" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="J43" s="39"/>
       <c r="K43" s="12" t="s">
@@ -2545,15 +2548,15 @@
       <c r="F44" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="3">
-        <v>4</v>
+      <c r="G44" s="44">
+        <v>2.53</v>
       </c>
       <c r="H44" s="12">
         <v>2.7</v>
       </c>
       <c r="I44" s="12">
         <f t="shared" si="1"/>
-        <v>1.2999999999999998</v>
+        <v>-0.17</v>
       </c>
       <c r="J44" s="39"/>
       <c r="K44" s="12" t="s">
@@ -2579,15 +2582,15 @@
       <c r="F45" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G45" s="3">
-        <v>1</v>
+      <c r="G45" s="44">
+        <v>0.22</v>
       </c>
       <c r="H45" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I45" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>-0.038</v>
       </c>
       <c r="J45" s="39"/>
       <c r="K45" s="12" t="s">
@@ -2615,15 +2618,15 @@
       <c r="F46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G46" s="3">
-        <v>2</v>
+      <c r="G46" s="44">
+        <v>1.89</v>
       </c>
       <c r="H46" s="12">
         <v>2.13</v>
       </c>
       <c r="I46" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>-0.24</v>
       </c>
       <c r="J46" s="39"/>
       <c r="K46" s="12" t="s">
@@ -2651,15 +2654,15 @@
       <c r="F47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G47" s="3">
-        <v>2</v>
+      <c r="G47" s="44">
+        <v>2.83</v>
       </c>
       <c r="H47" s="12">
         <v>1.28</v>
       </c>
       <c r="I47" s="12">
         <f t="shared" si="1"/>
-        <v>0.72</v>
+        <v>1.55</v>
       </c>
       <c r="J47" s="39"/>
       <c r="K47" s="12" t="s">
@@ -2687,15 +2690,15 @@
       <c r="F48" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G48" s="3">
-        <v>2</v>
+      <c r="G48" s="44">
+        <v>5.57</v>
       </c>
       <c r="H48" s="12">
         <v>0</v>
       </c>
       <c r="I48" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5.57</v>
       </c>
       <c r="J48" s="39"/>
       <c r="K48" s="12" t="s">
@@ -2723,15 +2726,15 @@
       <c r="F49" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G49" s="3">
-        <v>4</v>
+      <c r="G49" s="44">
+        <v>2.79</v>
       </c>
       <c r="H49" s="36">
         <v>2.13</v>
       </c>
       <c r="I49" s="12">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>0.66</v>
       </c>
       <c r="J49" s="40"/>
       <c r="K49" s="12" t="s">
@@ -2759,15 +2762,15 @@
       <c r="F50" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G50" s="3">
-        <v>1</v>
+      <c r="G50" s="44">
+        <v>0.11</v>
       </c>
       <c r="H50" s="36">
         <v>0.25800000000000001</v>
       </c>
       <c r="I50" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>-0.148</v>
       </c>
       <c r="J50" s="40"/>
       <c r="K50" s="12" t="s">
@@ -2795,15 +2798,15 @@
       <c r="F51" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G51" s="3">
-        <v>1</v>
+      <c r="G51" s="44">
+        <v>1.86</v>
       </c>
       <c r="H51" s="36">
         <v>2.13</v>
       </c>
       <c r="I51" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1299999999999999</v>
+        <v>-0.27</v>
       </c>
       <c r="J51" s="40"/>
       <c r="K51" s="12" t="s">
@@ -2831,15 +2834,15 @@
       <c r="F52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G52" s="3">
-        <v>4</v>
+      <c r="G52" s="44">
+        <v>5.96</v>
       </c>
       <c r="H52" s="36">
         <v>4.12</v>
       </c>
       <c r="I52" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12000000000000011</v>
+        <v>1.84</v>
       </c>
       <c r="J52" s="40"/>
       <c r="K52" s="12" t="s">
@@ -2867,15 +2870,15 @@
       <c r="F53" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G53" s="3">
-        <v>1</v>
+      <c r="G53" s="44">
+        <v>1.27</v>
       </c>
       <c r="H53" s="36">
         <v>0</v>
       </c>
       <c r="I53" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="J53" s="40"/>
       <c r="K53" s="12" t="s">
@@ -2903,15 +2906,15 @@
       <c r="F54" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G54" s="3">
-        <v>2</v>
+      <c r="G54" s="44">
+        <v>5.12</v>
       </c>
       <c r="H54" s="36">
         <v>2.13</v>
       </c>
       <c r="I54" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>2.99</v>
       </c>
       <c r="J54" s="40"/>
       <c r="K54" s="12" t="s">
@@ -2939,15 +2942,15 @@
       <c r="F55" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G55" s="3">
-        <v>3</v>
+      <c r="G55" s="44">
+        <v>2.96</v>
       </c>
       <c r="H55" s="36">
         <v>2.13</v>
       </c>
       <c r="I55" s="12">
         <f t="shared" si="1"/>
-        <v>0.87000000000000011</v>
+        <v>0.83</v>
       </c>
       <c r="J55" s="40"/>
       <c r="K55" s="12" t="s">
@@ -2975,15 +2978,15 @@
       <c r="F56" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="3">
-        <v>4</v>
+      <c r="G56" s="44">
+        <v>4.6</v>
       </c>
       <c r="H56" s="36">
         <v>1.28</v>
       </c>
       <c r="I56" s="12">
         <f t="shared" si="1"/>
-        <v>2.7199999999999998</v>
+        <v>3.32</v>
       </c>
       <c r="J56" s="40"/>
       <c r="K56" s="12" t="s">
@@ -3011,15 +3014,15 @@
       <c r="F57" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G57" s="3">
-        <v>5</v>
+      <c r="G57" s="44">
+        <v>4.03</v>
       </c>
       <c r="H57" s="36">
         <v>0</v>
       </c>
       <c r="I57" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.03</v>
       </c>
       <c r="J57" s="40"/>
       <c r="K57" s="12" t="s">
@@ -3047,15 +3050,15 @@
       <c r="F58" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G58" s="3">
-        <v>4</v>
+      <c r="G58" s="44">
+        <v>2.75</v>
       </c>
       <c r="H58" s="12">
         <v>2.13</v>
       </c>
       <c r="I58" s="12">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>0.62</v>
       </c>
       <c r="J58" s="39"/>
       <c r="K58" s="12" t="s">
@@ -3083,15 +3086,15 @@
       <c r="F59" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G59" s="3">
-        <v>1</v>
+      <c r="G59" s="44">
+        <v>0.12</v>
       </c>
       <c r="H59" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I59" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>-0.138</v>
       </c>
       <c r="J59" s="39"/>
       <c r="K59" s="12" t="s">
@@ -3119,15 +3122,15 @@
       <c r="F60" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G60" s="3">
-        <v>1</v>
+      <c r="G60" s="44">
+        <v>1.82</v>
       </c>
       <c r="H60" s="12">
         <v>2.13</v>
       </c>
       <c r="I60" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1299999999999999</v>
+        <v>-0.31</v>
       </c>
       <c r="J60" s="39"/>
       <c r="K60" s="12" t="s">
@@ -3155,15 +3158,15 @@
       <c r="F61" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G61" s="3">
-        <v>4</v>
+      <c r="G61" s="44">
+        <v>4.07</v>
       </c>
       <c r="H61" s="12">
         <v>4.12</v>
       </c>
       <c r="I61" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12000000000000011</v>
+        <v>-0.05</v>
       </c>
       <c r="J61" s="39"/>
       <c r="K61" s="12" t="s">
@@ -3191,15 +3194,15 @@
       <c r="F62" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G62" s="3">
-        <v>1</v>
+      <c r="G62" s="44">
+        <v>1.27</v>
       </c>
       <c r="H62" s="12">
         <v>0</v>
       </c>
       <c r="I62" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="J62" s="39"/>
       <c r="K62" s="12" t="s">
@@ -3227,15 +3230,15 @@
       <c r="F63" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G63" s="3">
-        <v>2</v>
+      <c r="G63" s="44">
+        <v>2.53</v>
       </c>
       <c r="H63" s="12">
         <v>2.13</v>
       </c>
       <c r="I63" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>0.4</v>
       </c>
       <c r="J63" s="39"/>
       <c r="K63" s="12" t="s">
@@ -3263,15 +3266,15 @@
       <c r="F64" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G64" s="3">
-        <v>3</v>
+      <c r="G64" s="44">
+        <v>3.11</v>
       </c>
       <c r="H64" s="12">
         <v>2.13</v>
       </c>
       <c r="I64" s="12">
         <f t="shared" si="1"/>
-        <v>0.87000000000000011</v>
+        <v>0.98</v>
       </c>
       <c r="J64" s="39"/>
       <c r="K64" s="12" t="s">
@@ -3299,15 +3302,15 @@
       <c r="F65" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G65" s="3">
-        <v>4</v>
+      <c r="G65" s="44">
+        <v>4.19</v>
       </c>
       <c r="H65" s="12">
         <v>1.28</v>
       </c>
       <c r="I65" s="12">
         <f t="shared" si="1"/>
-        <v>2.7199999999999998</v>
+        <v>2.91</v>
       </c>
       <c r="J65" s="39"/>
       <c r="K65" s="12" t="s">
@@ -3335,15 +3338,15 @@
       <c r="F66" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G66" s="3">
-        <v>5</v>
+      <c r="G66" s="44">
+        <v>4.68</v>
       </c>
       <c r="H66" s="12">
         <v>0</v>
       </c>
       <c r="I66" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.68</v>
       </c>
       <c r="J66" s="39"/>
       <c r="K66" s="12" t="s">
@@ -3371,15 +3374,15 @@
       <c r="F67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G67" s="3">
-        <v>4</v>
+      <c r="G67" s="44">
+        <v>2.73</v>
       </c>
       <c r="H67" s="12">
         <v>2.13</v>
       </c>
       <c r="I67" s="12">
         <f t="shared" si="1"/>
-        <v>1.87</v>
+        <v>0.6</v>
       </c>
       <c r="J67" s="39"/>
       <c r="K67" s="12" t="s">
@@ -3407,15 +3410,15 @@
       <c r="F68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G68" s="3">
-        <v>1</v>
+      <c r="G68" s="44">
+        <v>2.98</v>
       </c>
       <c r="H68" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I68" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>2.722</v>
       </c>
       <c r="J68" s="39"/>
       <c r="K68" s="12" t="s">
@@ -3443,15 +3446,15 @@
       <c r="F69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G69" s="3">
-        <v>1</v>
+      <c r="G69" s="44">
+        <v>2.88</v>
       </c>
       <c r="H69" s="12">
         <v>2.13</v>
       </c>
       <c r="I69" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1299999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J69" s="39"/>
       <c r="K69" s="12" t="s">
@@ -3479,8 +3482,8 @@
       <c r="F70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G70" s="3">
-        <v>3</v>
+      <c r="G70" s="44">
+        <v>3.0</v>
       </c>
       <c r="H70" s="12">
         <v>1.28</v>
@@ -3515,15 +3518,15 @@
       <c r="F71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G71" s="3">
-        <v>2</v>
+      <c r="G71" s="44">
+        <v>2.58</v>
       </c>
       <c r="H71" s="12">
         <v>0</v>
       </c>
       <c r="I71" s="12">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="J71" s="39"/>
       <c r="K71" s="12" t="s">
@@ -3549,15 +3552,15 @@
       <c r="F72" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G72" s="3">
-        <v>2</v>
+      <c r="G72" s="44">
+        <v>4.1</v>
       </c>
       <c r="H72" s="12">
         <v>2.13</v>
       </c>
       <c r="I72" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>1.97</v>
       </c>
       <c r="J72" s="39"/>
       <c r="K72" s="12" t="s">
@@ -3583,15 +3586,15 @@
       <c r="F73" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G73" s="3">
-        <v>3</v>
+      <c r="G73" s="44">
+        <v>1.78</v>
       </c>
       <c r="H73" s="12">
         <v>2.13</v>
       </c>
       <c r="I73" s="12">
         <f t="shared" si="1"/>
-        <v>0.87000000000000011</v>
+        <v>-0.35</v>
       </c>
       <c r="J73" s="39"/>
       <c r="K73" s="12" t="s">
@@ -3617,15 +3620,15 @@
       <c r="F74" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G74" s="3">
-        <v>4</v>
+      <c r="G74" s="44">
+        <v>4.37</v>
       </c>
       <c r="H74" s="12">
         <v>1.28</v>
       </c>
       <c r="I74" s="12">
         <f t="shared" si="1"/>
-        <v>2.7199999999999998</v>
+        <v>3.09</v>
       </c>
       <c r="J74" s="39"/>
       <c r="K74" s="12" t="s">
@@ -3653,15 +3656,15 @@
       <c r="F75" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G75" s="3">
-        <v>5</v>
+      <c r="G75" s="44">
+        <v>4.7</v>
       </c>
       <c r="H75" s="12">
         <v>0</v>
       </c>
       <c r="I75" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J75" s="39"/>
       <c r="K75" s="12" t="s">
@@ -3689,15 +3692,15 @@
       <c r="F76" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G76" s="3">
-        <v>8</v>
+      <c r="G76" s="44">
+        <v>3.29</v>
       </c>
       <c r="H76" s="12">
         <v>2.13</v>
       </c>
       <c r="I76" s="37">
         <f t="shared" si="1"/>
-        <v>5.87</v>
+        <v>1.16</v>
       </c>
       <c r="J76" s="39"/>
       <c r="K76" s="12" t="s">
@@ -3725,15 +3728,15 @@
       <c r="F77" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G77" s="3">
-        <v>2</v>
+      <c r="G77" s="44">
+        <v>3.46</v>
       </c>
       <c r="H77" s="12">
         <v>2.13</v>
       </c>
       <c r="I77" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>1.33</v>
       </c>
       <c r="J77" s="39"/>
       <c r="K77" s="12" t="s">
@@ -3761,15 +3764,15 @@
       <c r="F78" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G78" s="3">
-        <v>1</v>
+      <c r="G78" s="44">
+        <v>0.98</v>
       </c>
       <c r="H78" s="12">
         <v>0</v>
       </c>
       <c r="I78" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J78" s="39"/>
       <c r="K78" s="12" t="s">
@@ -3797,15 +3800,15 @@
       <c r="F79" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G79" s="3">
-        <v>7</v>
+      <c r="G79" s="44">
+        <v>6.44</v>
       </c>
       <c r="H79" s="12">
         <v>2.13</v>
       </c>
       <c r="I79" s="37">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>4.31</v>
       </c>
       <c r="J79" s="39"/>
       <c r="K79" s="12" t="s">
@@ -3833,15 +3836,15 @@
       <c r="F80" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G80" s="3">
-        <v>3</v>
+      <c r="G80" s="44">
+        <v>3.04</v>
       </c>
       <c r="H80" s="12">
         <v>4.12</v>
       </c>
       <c r="I80" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.08</v>
       </c>
       <c r="J80" s="39"/>
       <c r="K80" s="12" t="s">
@@ -3867,15 +3870,15 @@
       <c r="F81" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="G81" s="3">
-        <v>7</v>
+      <c r="G81" s="44">
+        <v>6.44</v>
       </c>
       <c r="H81" s="12">
         <v>2.13</v>
       </c>
       <c r="I81" s="37">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>4.31</v>
       </c>
       <c r="J81" s="39"/>
       <c r="K81" s="12" t="s">
@@ -3903,15 +3906,15 @@
       <c r="F82" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G82" s="3">
-        <v>7</v>
+      <c r="G82" s="44">
+        <v>5.21</v>
       </c>
       <c r="H82" s="12">
         <v>2.13</v>
       </c>
       <c r="I82" s="37">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>3.08</v>
       </c>
       <c r="J82" s="39"/>
       <c r="K82" s="12" t="s">
@@ -3939,15 +3942,15 @@
       <c r="F83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G83" s="3">
-        <v>1</v>
+      <c r="G83" s="44">
+        <v>0.38</v>
       </c>
       <c r="H83" s="12">
         <v>0.25800000000000001</v>
       </c>
       <c r="I83" s="12">
         <f t="shared" si="1"/>
-        <v>0.74199999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="J83" s="39"/>
       <c r="K83" s="12" t="s">
@@ -3975,15 +3978,15 @@
       <c r="F84" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G84" s="3">
-        <v>2</v>
+      <c r="G84" s="44">
+        <v>1.67</v>
       </c>
       <c r="H84" s="12">
         <v>2.13</v>
       </c>
       <c r="I84" s="12">
         <f t="shared" si="1"/>
-        <v>-0.12999999999999989</v>
+        <v>-0.46</v>
       </c>
       <c r="J84" s="39"/>
       <c r="K84" s="12" t="s">
@@ -4011,15 +4014,15 @@
       <c r="F85" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G85" s="3">
-        <v>3</v>
+      <c r="G85" s="44">
+        <v>2.79</v>
       </c>
       <c r="H85" s="12">
         <v>1.28</v>
       </c>
       <c r="I85" s="12">
         <f t="shared" si="1"/>
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="J85" s="39"/>
       <c r="K85" s="12" t="s">
@@ -4047,15 +4050,15 @@
       <c r="F86" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G86" s="3">
-        <v>1</v>
+      <c r="G86" s="44">
+        <v>1.3</v>
       </c>
       <c r="H86" s="12">
         <v>0</v>
       </c>
       <c r="I86" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J86" s="39"/>
       <c r="K86" s="12" t="s">
@@ -4083,15 +4086,15 @@
       <c r="F87" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G87" s="3">
-        <v>7</v>
+      <c r="G87" s="44">
+        <v>5.21</v>
       </c>
       <c r="H87" s="12">
         <v>2.13</v>
       </c>
       <c r="I87" s="37">
         <f t="shared" si="1"/>
-        <v>4.87</v>
+        <v>3.08</v>
       </c>
       <c r="J87" s="39"/>
       <c r="K87" s="12" t="s">
@@ -4119,15 +4122,15 @@
       <c r="F88" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G88" s="3">
-        <v>8</v>
+      <c r="G88" s="44">
+        <v>6.58</v>
       </c>
       <c r="H88" s="12">
         <v>4.12</v>
       </c>
       <c r="I88" s="37">
         <f t="shared" si="1"/>
-        <v>3.88</v>
+        <v>2.46</v>
       </c>
       <c r="J88" s="39"/>
       <c r="K88" s="12" t="s">
@@ -4155,15 +4158,15 @@
       <c r="F89" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G89" s="3">
-        <v>5</v>
+      <c r="G89" s="44">
+        <v>6.16</v>
       </c>
       <c r="H89" s="12">
         <v>1.28</v>
       </c>
       <c r="I89" s="37">
         <f t="shared" si="1"/>
-        <v>3.7199999999999998</v>
+        <v>4.88</v>
       </c>
       <c r="J89" s="39"/>
       <c r="K89" s="12" t="s">
@@ -4191,15 +4194,15 @@
       <c r="F90" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G90" s="3">
-        <v>1</v>
+      <c r="G90" s="44">
+        <v>0.48</v>
       </c>
       <c r="H90" s="12">
         <v>0</v>
       </c>
       <c r="I90" s="12">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="J90" s="39"/>
       <c r="K90" s="12" t="s">
